--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484041_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484041_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1702</v>
+        <v>2.8311</v>
       </c>
       <c r="E2" t="n">
-        <v>2.2992</v>
+        <v>1.381</v>
       </c>
       <c r="F2" t="n">
-        <v>1.871</v>
+        <v>1.4501</v>
       </c>
       <c r="G2" t="n">
         <v>1.0277</v>
@@ -610,13 +610,13 @@
         <v>1.3887</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8053</v>
+        <v>0.4662</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1678</v>
+        <v>0.2495</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6375</v>
+        <v>0.2167</v>
       </c>
       <c r="V2" t="n">
         <v>0.9405</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8784</v>
+        <v>0.761</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3489</v>
+        <v>1.8387</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.4705</v>
+        <v>-1.0777</v>
       </c>
       <c r="G3" t="n">
         <v>1.0094</v>
@@ -688,13 +688,13 @@
         <v>1.5871</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5624</v>
+        <v>0.445</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7427</v>
+        <v>0.2325</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1803</v>
+        <v>0.2125</v>
       </c>
       <c r="V3" t="n">
         <v>0.6954</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.745</v>
+        <v>-1.3446</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.2918</v>
+        <v>-2.0878</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5468</v>
+        <v>0.7432</v>
       </c>
       <c r="G4" t="n">
         <v>-1.3606</v>
@@ -766,13 +766,13 @@
         <v>0.1984</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3168</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3117</v>
+        <v>-0.1077</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0051</v>
+        <v>0.1913</v>
       </c>
       <c r="V4" t="n">
         <v>-0.266</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.2753</v>
+        <v>-1.4514</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.9225</v>
+        <v>-1.9022</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6473</v>
+        <v>0.4509</v>
       </c>
       <c r="G5" t="n">
         <v>-1.2502</v>
@@ -844,13 +844,13 @@
         <v>2.579</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.403</v>
+        <v>0.4209</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8047</v>
+        <v>0.2156</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4017</v>
+        <v>0.2053</v>
       </c>
       <c r="V5" t="n">
         <v>0.7665999999999999</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.4871</v>
+        <v>-2.607</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.0796</v>
+        <v>-2.2836</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4075</v>
+        <v>-0.3233</v>
       </c>
       <c r="G6" t="n">
         <v>-3.214</v>
@@ -922,13 +922,13 @@
         <v>0.7935</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7817</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.3458</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2318</v>
+        <v>0.316</v>
       </c>
       <c r="V6" t="n">
         <v>-0.8483000000000001</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.2191</v>
+        <v>-4.678</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3043</v>
+        <v>-1.4266</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.9148</v>
+        <v>-3.2514</v>
       </c>
       <c r="G7" t="n">
         <v>-4.1221</v>
@@ -1000,13 +1000,13 @@
         <v>1.1903</v>
       </c>
       <c r="S7" t="n">
-        <v>2.4736</v>
+        <v>1.0147</v>
       </c>
       <c r="T7" t="n">
-        <v>1.797</v>
+        <v>0.6746</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6767</v>
+        <v>0.34</v>
       </c>
       <c r="V7" t="n">
         <v>-0.7771</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.24</v>
+        <v>-4.7274</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.4576</v>
+        <v>-3.2535</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.7825</v>
+        <v>-1.4739</v>
       </c>
       <c r="G8" t="n">
         <v>-2.6712</v>
@@ -1078,13 +1078,13 @@
         <v>1.5871</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7917999999999999</v>
+        <v>-0.2791</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3173</v>
+        <v>-0.1133</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4745</v>
+        <v>-0.1658</v>
       </c>
       <c r="V8" t="n">
         <v>-1.3803</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.7064</v>
+        <v>-5.9206</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.2079</v>
+        <v>-3.3099</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.4985</v>
+        <v>-2.6107</v>
       </c>
       <c r="G9" t="n">
         <v>-2.7851</v>
@@ -1156,13 +1156,13 @@
         <v>1.9838</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1463</v>
+        <v>-0.068</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3119</v>
+        <v>0.2098</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1656</v>
+        <v>-0.2778</v>
       </c>
       <c r="V9" t="n">
         <v>-2.0757</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.742</v>
+        <v>-6.2599</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.9517</v>
+        <v>-3.4415</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.7903</v>
+        <v>-2.8183</v>
       </c>
       <c r="G10" t="n">
         <v>-2.0196</v>
@@ -1234,13 +1234,13 @@
         <v>0.1984</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7385</v>
+        <v>-0.2565</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.1133</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1151</v>
+        <v>-0.1432</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2065</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.8863</v>
+        <v>-7.8559</v>
       </c>
       <c r="E11" t="n">
-        <v>-9.430999999999999</v>
+        <v>-8.5128</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5447</v>
+        <v>0.6569</v>
       </c>
       <c r="G11" t="n">
         <v>-2.8574</v>
@@ -1312,13 +1312,13 @@
         <v>2.3806</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2515</v>
+        <v>-0.221</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2356</v>
+        <v>-0.3173</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.016</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2065</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-31.2526</v>
+        <v>-31.2527</v>
       </c>
       <c r="E12" t="n">
-        <v>-22.9983</v>
+        <v>-22.9982</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.254299999999999</v>
+        <v>-8.254200000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-18.2431</v>
@@ -1390,13 +1390,13 @@
         <v>13.8869</v>
       </c>
       <c r="S12" t="n">
-        <v>2.2677</v>
+        <v>2.2676</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2765</v>
+        <v>1.2762</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9910999999999999</v>
+        <v>0.9912000000000002</v>
       </c>
       <c r="V12" t="n">
         <v>-5.357900000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.5235</v>
+        <v>7.4597</v>
       </c>
       <c r="E13" t="n">
-        <v>5.1294</v>
+        <v>4.9254</v>
       </c>
       <c r="F13" t="n">
-        <v>2.394</v>
+        <v>2.5343</v>
       </c>
       <c r="G13" t="n">
         <v>4.3081</v>
@@ -1468,13 +1468,13 @@
         <v>1.7855</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0425</v>
+        <v>-0.1063</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0567</v>
+        <v>-0.1473</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0993</v>
+        <v>0.041</v>
       </c>
       <c r="V13" t="n">
         <v>1.4724</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.3939</v>
+        <v>5.132</v>
       </c>
       <c r="E14" t="n">
-        <v>3.625</v>
+        <v>3.1149</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7689</v>
+        <v>2.0171</v>
       </c>
       <c r="G14" t="n">
         <v>3.466</v>
@@ -1546,13 +1546,13 @@
         <v>1.9838</v>
       </c>
       <c r="S14" t="n">
-        <v>0.67</v>
+        <v>0.4081</v>
       </c>
       <c r="T14" t="n">
-        <v>0.924</v>
+        <v>0.4138</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.254</v>
+        <v>-0.0057</v>
       </c>
       <c r="V14" t="n">
         <v>0.266</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. MULIO CAMPOS</t>
+          <t>J. ARNAL DIAZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3924</v>
+        <v>4.9242</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7652</v>
+        <v>1.5761</v>
       </c>
       <c r="F15" t="n">
-        <v>3.6272</v>
+        <v>3.3481</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8625</v>
+        <v>1.2427</v>
       </c>
       <c r="H15" t="n">
-        <v>3.1295</v>
+        <v>1.9098</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.2671</v>
+        <v>-0.6672</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6808999999999999</v>
+        <v>0.3332</v>
       </c>
       <c r="K15" t="n">
-        <v>1.961</v>
+        <v>1.0134</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.2801</v>
+        <v>-0.6802</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1815</v>
+        <v>0.9095</v>
       </c>
       <c r="N15" t="n">
-        <v>1.1685</v>
+        <v>0.8965</v>
       </c>
       <c r="O15" t="n">
         <v>0.013</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3887</v>
+        <v>1.9838</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3806</v>
+        <v>1.9838</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.7865</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1303</v>
+        <v>-0.5667</v>
       </c>
       <c r="U15" t="n">
-        <v>0.06510000000000001</v>
+        <v>-0.2197</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2065</v>
+        <v>2.4842</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2065</v>
+        <v>1.8097</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. ARNAL DIAZ</t>
+          <t>P. MULIO CAMPOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,75 +1657,71 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.3656</v>
+        <v>4.0481</v>
       </c>
       <c r="E16" t="n">
-        <v>1.27</v>
+        <v>0.5611</v>
       </c>
       <c r="F16" t="n">
-        <v>3.0956</v>
+        <v>3.487</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2427</v>
+        <v>1.8625</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9098</v>
+        <v>3.1295</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6672</v>
+        <v>-1.2671</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3332</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0134</v>
+        <v>1.961</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6802</v>
+        <v>-1.2801</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9095</v>
+        <v>1.1815</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8965</v>
+        <v>1.1685</v>
       </c>
       <c r="O16" t="n">
         <v>0.013</v>
       </c>
       <c r="P16" t="n">
-        <v>1.9838</v>
+        <v>1.3887</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9838</v>
+        <v>2.3806</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.345</v>
+        <v>-0.4096</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8728</v>
+        <v>-0.3344</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4722</v>
+        <v>-0.0752</v>
       </c>
       <c r="V16" t="n">
-        <v>2.4842</v>
+        <v>1.2065</v>
       </c>
       <c r="W16" t="n">
-        <v>1.8097</v>
+        <v>1.2065</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>D. TUGORES SOTO</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -1735,64 +1731,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.0779</v>
+        <v>3.7393</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8633</v>
+        <v>0.0205</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2146</v>
+        <v>3.7188</v>
       </c>
       <c r="G17" t="n">
-        <v>2.498</v>
+        <v>1.8093</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7284</v>
+        <v>0.8661</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7696</v>
+        <v>0.9432</v>
       </c>
       <c r="J17" t="n">
-        <v>2.6491</v>
+        <v>0.4229</v>
       </c>
       <c r="K17" t="n">
-        <v>2.0416</v>
+        <v>0.3024</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6075</v>
+        <v>0.1205</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1512</v>
+        <v>1.3864</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3132</v>
+        <v>0.5637</v>
       </c>
       <c r="O17" t="n">
-        <v>0.162</v>
+        <v>0.8227</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3968</v>
+        <v>2.579</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3806</v>
+        <v>2.579</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0828</v>
+        <v>-0.649</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0679</v>
+        <v>-0.4024</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0149</v>
+        <v>-0.2467</v>
       </c>
       <c r="V17" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1797,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>,. VICENTE SABARIEGO</t>
+          <t>. VICENTE SABARIEGO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,71 +1809,75 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.9322</v>
+        <v>3.7393</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4958</v>
+        <v>0.0205</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4364</v>
+        <v>3.7188</v>
       </c>
       <c r="G18" t="n">
-        <v>1.9638</v>
+        <v>1.8093</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3614</v>
+        <v>0.8661</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6024</v>
+        <v>0.9432</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9638</v>
+        <v>0.4229</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3614</v>
+        <v>0.3024</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6024</v>
+        <v>0.1205</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.3864</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>0.5637</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.8227</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.579</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.579</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4364</v>
+        <v>-0.649</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.4024</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4364</v>
+        <v>-0.2467</v>
       </c>
       <c r="V18" t="n">
-        <v>0.532</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.532</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>D. TUGORES SOTO</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -1887,64 +1887,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.8262</v>
+        <v>3.3619</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3876</v>
+        <v>1.0674</v>
       </c>
       <c r="F19" t="n">
-        <v>3.2138</v>
+        <v>2.2945</v>
       </c>
       <c r="G19" t="n">
-        <v>1.8093</v>
+        <v>2.498</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8661</v>
+        <v>1.7284</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9432</v>
+        <v>0.7696</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4229</v>
+        <v>2.6491</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3024</v>
+        <v>2.0416</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1205</v>
+        <v>0.6075</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3864</v>
+        <v>-0.1512</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5637</v>
+        <v>-0.3132</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8227</v>
+        <v>0.162</v>
       </c>
       <c r="P19" t="n">
-        <v>2.579</v>
+        <v>0.3968</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R19" t="n">
-        <v>2.579</v>
+        <v>2.3806</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5621</v>
+        <v>0.2012</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8105</v>
+        <v>0.1361</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7516</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1953,7 +1953,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>. VICENTE SABARIEGO</t>
+          <t>,. VICENTE SABARIEGO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1965,64 +1965,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.8262</v>
+        <v>2.7452</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3876</v>
+        <v>2.4958</v>
       </c>
       <c r="F20" t="n">
-        <v>3.2138</v>
+        <v>0.2494</v>
       </c>
       <c r="G20" t="n">
-        <v>1.8093</v>
+        <v>1.9638</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8661</v>
+        <v>1.3614</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9432</v>
+        <v>0.6024</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4229</v>
+        <v>1.9638</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3024</v>
+        <v>1.3614</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1205</v>
+        <v>0.6024</v>
       </c>
       <c r="M20" t="n">
-        <v>1.3864</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5637</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8227</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.579</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.579</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5621</v>
+        <v>0.2494</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8105</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7516</v>
+        <v>0.2494</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.532</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.532</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2043,13 +2043,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.439</v>
+        <v>2.5419</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9334</v>
+        <v>-0.3212</v>
       </c>
       <c r="F21" t="n">
-        <v>3.3724</v>
+        <v>2.8631</v>
       </c>
       <c r="G21" t="n">
         <v>1.813</v>
@@ -2088,13 +2088,13 @@
         <v>3.3725</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6401</v>
+        <v>-0.5371</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2469</v>
+        <v>-0.6347</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6068</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>0.8692</v>
@@ -2121,13 +2121,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.6492</v>
+        <v>1.1246</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0983</v>
+        <v>-0.5064</v>
       </c>
       <c r="F22" t="n">
-        <v>1.7475</v>
+        <v>1.6311</v>
       </c>
       <c r="G22" t="n">
         <v>0.1204</v>
@@ -2166,13 +2166,13 @@
         <v>1.5871</v>
       </c>
       <c r="S22" t="n">
-        <v>1.3223</v>
+        <v>0.7978</v>
       </c>
       <c r="T22" t="n">
-        <v>0.924</v>
+        <v>0.5159</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3984</v>
+        <v>0.2819</v>
       </c>
       <c r="V22" t="n">
         <v>0.6032</v>
@@ -2187,7 +2187,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. MAÑES CARRETERO</t>
+          <t>P. SAIZ FUENTES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2199,73 +2199,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.5854</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3658</v>
+        <v>1.0436</v>
       </c>
       <c r="F23" t="n">
-        <v>1.8775</v>
+        <v>-0.4581</v>
       </c>
       <c r="G23" t="n">
-        <v>1.6514</v>
+        <v>-0.1806</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2899</v>
+        <v>0.6602</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3615</v>
+        <v>-0.8408</v>
       </c>
       <c r="J23" t="n">
-        <v>1.3386</v>
+        <v>0.3836</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7311</v>
+        <v>0.9784</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6075</v>
+        <v>-0.5948</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3127</v>
+        <v>-0.5642</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5588</v>
+        <v>-0.3181</v>
       </c>
       <c r="O23" t="n">
         <v>-0.2461</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.9838</v>
+        <v>2.1822</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.9677</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.9838</v>
+        <v>2.1822</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0964</v>
+        <v>-0.2097</v>
       </c>
       <c r="T23" t="n">
         <v>0.0567</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1531</v>
+        <v>-0.2665</v>
       </c>
       <c r="V23" t="n">
-        <v>0.9405</v>
+        <v>-1.2065</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2065</v>
+        <v>0.6032</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.266</v>
+        <v>-1.8097</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. SAIZ FUENTES</t>
+          <t>M. MAÑES CARRETERO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2277,67 +2277,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2249</v>
+        <v>0.4096</v>
       </c>
       <c r="E24" t="n">
-        <v>1.0436</v>
+        <v>-1.4679</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8186</v>
+        <v>1.8775</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1806</v>
+        <v>1.6514</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6602</v>
+        <v>1.2899</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8408</v>
+        <v>0.3615</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3836</v>
+        <v>1.3386</v>
       </c>
       <c r="K24" t="n">
-        <v>0.9784</v>
+        <v>0.7311</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5948</v>
+        <v>0.6075</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5642</v>
+        <v>0.3127</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3181</v>
+        <v>0.5588</v>
       </c>
       <c r="O24" t="n">
         <v>-0.2461</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1822</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-3.9677</v>
       </c>
       <c r="R24" t="n">
-        <v>2.1822</v>
+        <v>1.9838</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5702</v>
+        <v>-0.1984</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0567</v>
+        <v>-0.0453</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.627</v>
+        <v>-0.1531</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2065</v>
+        <v>0.9405</v>
       </c>
       <c r="W24" t="n">
-        <v>0.6032</v>
+        <v>1.2065</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.8097</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="25">
@@ -2355,13 +2355,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.0839</v>
+        <v>-4.0456</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.1528</v>
+        <v>-4.2549</v>
       </c>
       <c r="F25" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.2092</v>
       </c>
       <c r="G25" t="n">
         <v>-2.3115</v>
@@ -2400,13 +2400,13 @@
         <v>1.5871</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2919</v>
+        <v>-0.2537</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1191</v>
+        <v>0.0171</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.411</v>
+        <v>-0.2707</v>
       </c>
       <c r="V25" t="n">
         <v>-2.0757</v>
@@ -2433,13 +2433,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>34.0787</v>
+        <v>35.76559999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>7.866799999999999</v>
+        <v>8.274900000000002</v>
       </c>
       <c r="F26" t="n">
-        <v>26.2121</v>
+        <v>27.4908</v>
       </c>
       <c r="G26" t="n">
         <v>20.0524</v>
@@ -2460,10 +2460,10 @@
         <v>-2.1153</v>
       </c>
       <c r="M26" t="n">
-        <v>6.538100000000001</v>
+        <v>6.538099999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>4.840299999999999</v>
+        <v>4.8403</v>
       </c>
       <c r="O26" t="n">
         <v>1.6978</v>
@@ -2478,13 +2478,13 @@
         <v>26.385</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.829599999999999</v>
+        <v>-2.1428</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.8017</v>
+        <v>-1.3936</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.028</v>
+        <v>-0.7493000000000001</v>
       </c>
       <c r="V26" t="n">
         <v>5.357800000000001</v>
